--- a/public/sap-reporting/expansion-150-downloads/EXT-QM07-01.xlsx
+++ b/public/sap-reporting/expansion-150-downloads/EXT-QM07-01.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="R564180f2512d4990"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="R7fe5cefc166f4f25"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="R76f2ff9b8c9f4c71"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="R8a631f2f82244bde"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="Rfd7800dcc5f241a9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="R0fce15a7bbd74444"/>
   </x:sheets>
 </x:workbook>
 </file>
